--- a/Teachers_and_School_Patrons_Extract.xlsx
+++ b/Teachers_and_School_Patrons_Extract.xlsx
@@ -493,7 +493,7 @@
     <t>Angella peter and Otiema Salume</t>
   </si>
   <si>
-    <t>JACKSON SANDE</t>
+    <t>JACKSON SANDE / Sande Jackson and Chekwech Nasta</t>
   </si>
   <si>
     <t>YEKO FLOMENA</t>
@@ -532,7 +532,7 @@
     <t>Denis</t>
   </si>
   <si>
-    <t>Akwii ochan</t>
+    <t>Akwii ochan / Gabriel</t>
   </si>
   <si>
     <t>No</t>
@@ -2063,7 +2063,7 @@
         <v>159</v>
       </c>
       <c r="E51">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="F51" t="s">
         <v>174</v>
@@ -2316,7 +2316,7 @@
         <v>169</v>
       </c>
       <c r="E62">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F62" t="s">
         <v>174</v>
@@ -2385,7 +2385,7 @@
         <v>172</v>
       </c>
       <c r="E65">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F65" t="s">
         <v>173</v>

--- a/Teachers_and_School_Patrons_Extract.xlsx
+++ b/Teachers_and_School_Patrons_Extract.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="176">
   <si>
     <t>District</t>
   </si>
@@ -506,6 +506,9 @@
   </si>
   <si>
     <t>Tukei Clement and kaptengan Leonard</t>
+  </si>
+  <si>
+    <t>Kauke Laban, Mateba kennedy</t>
   </si>
   <si>
     <t>Oonyu Julious and Lochoro christine</t>
@@ -939,10 +942,10 @@
         <v>41</v>
       </c>
       <c r="F2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -962,10 +965,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -985,10 +988,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1008,10 +1011,10 @@
         <v>41</v>
       </c>
       <c r="F5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1031,10 +1034,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1054,10 +1057,10 @@
         <v>41</v>
       </c>
       <c r="F7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1077,10 +1080,10 @@
         <v>41</v>
       </c>
       <c r="F8" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1100,10 +1103,10 @@
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1123,10 +1126,10 @@
         <v>41</v>
       </c>
       <c r="F10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1146,10 +1149,10 @@
         <v>60</v>
       </c>
       <c r="F11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1169,10 +1172,10 @@
         <v>65</v>
       </c>
       <c r="F12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1192,10 +1195,10 @@
         <v>60</v>
       </c>
       <c r="F13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1215,10 +1218,10 @@
         <v>53</v>
       </c>
       <c r="F14" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G14" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1238,10 +1241,10 @@
         <v>54</v>
       </c>
       <c r="F15" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G15" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1261,10 +1264,10 @@
         <v>30</v>
       </c>
       <c r="F16" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G16" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1284,10 +1287,10 @@
         <v>35</v>
       </c>
       <c r="F17" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G17" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1307,10 +1310,10 @@
         <v>41</v>
       </c>
       <c r="F18" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G18" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1330,10 +1333,10 @@
         <v>41</v>
       </c>
       <c r="F19" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G19" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1353,10 +1356,10 @@
         <v>0</v>
       </c>
       <c r="F20" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G20" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1376,10 +1379,10 @@
         <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G21" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1399,10 +1402,10 @@
         <v>41</v>
       </c>
       <c r="F22" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G22" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1422,10 +1425,10 @@
         <v>0</v>
       </c>
       <c r="F23" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G23" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1445,10 +1448,10 @@
         <v>41</v>
       </c>
       <c r="F24" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G24" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1468,10 +1471,10 @@
         <v>0</v>
       </c>
       <c r="F25" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G25" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1491,10 +1494,10 @@
         <v>30</v>
       </c>
       <c r="F26" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G26" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1514,10 +1517,10 @@
         <v>30</v>
       </c>
       <c r="F27" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G27" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1537,10 +1540,10 @@
         <v>41</v>
       </c>
       <c r="F28" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G28" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1560,10 +1563,10 @@
         <v>41</v>
       </c>
       <c r="F29" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G29" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1583,10 +1586,10 @@
         <v>41</v>
       </c>
       <c r="F30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1606,10 +1609,10 @@
         <v>41</v>
       </c>
       <c r="F31" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G31" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1629,10 +1632,10 @@
         <v>41</v>
       </c>
       <c r="F32" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G32" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1652,10 +1655,10 @@
         <v>41</v>
       </c>
       <c r="F33" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G33" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1675,10 +1678,10 @@
         <v>41</v>
       </c>
       <c r="F34" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G34" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1698,10 +1701,10 @@
         <v>41</v>
       </c>
       <c r="F35" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G35" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1721,10 +1724,10 @@
         <v>0</v>
       </c>
       <c r="F36" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G36" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1744,10 +1747,10 @@
         <v>41</v>
       </c>
       <c r="F37" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G37" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1767,10 +1770,10 @@
         <v>0</v>
       </c>
       <c r="F38" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G38" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1787,13 +1790,13 @@
         <v>147</v>
       </c>
       <c r="E39">
-        <v>41</v>
+        <v>70</v>
       </c>
       <c r="F39" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G39" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1813,10 +1816,10 @@
         <v>41</v>
       </c>
       <c r="F40" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G40" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1836,10 +1839,10 @@
         <v>41</v>
       </c>
       <c r="F41" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G41" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1859,10 +1862,10 @@
         <v>28</v>
       </c>
       <c r="F42" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G42" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1882,10 +1885,10 @@
         <v>41</v>
       </c>
       <c r="F43" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G43" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1905,10 +1908,10 @@
         <v>41</v>
       </c>
       <c r="F44" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G44" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1928,10 +1931,10 @@
         <v>41</v>
       </c>
       <c r="F45" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G45" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1951,10 +1954,10 @@
         <v>41</v>
       </c>
       <c r="F46" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G46" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1974,10 +1977,10 @@
         <v>41</v>
       </c>
       <c r="F47" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G47" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1997,10 +2000,10 @@
         <v>41</v>
       </c>
       <c r="F48" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G48" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2020,10 +2023,10 @@
         <v>40</v>
       </c>
       <c r="F49" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G49" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2043,10 +2046,10 @@
         <v>41</v>
       </c>
       <c r="F50" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G50" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2066,10 +2069,10 @@
         <v>60</v>
       </c>
       <c r="F51" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G51" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2089,10 +2092,10 @@
         <v>60</v>
       </c>
       <c r="F52" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G52" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2112,10 +2115,10 @@
         <v>60</v>
       </c>
       <c r="F53" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G53" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -2135,10 +2138,10 @@
         <v>55</v>
       </c>
       <c r="F54" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G54" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2158,10 +2161,10 @@
         <v>68</v>
       </c>
       <c r="F55" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G55" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -2175,16 +2178,16 @@
         <v>113</v>
       </c>
       <c r="D56" t="s">
-        <v>124</v>
+        <v>164</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="F56" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G56" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -2198,16 +2201,16 @@
         <v>114</v>
       </c>
       <c r="D57" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E57">
         <v>41</v>
       </c>
       <c r="F57" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G57" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -2221,16 +2224,16 @@
         <v>115</v>
       </c>
       <c r="D58" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E58">
         <v>41</v>
       </c>
       <c r="F58" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G58" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -2244,16 +2247,16 @@
         <v>116</v>
       </c>
       <c r="D59" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E59">
         <v>41</v>
       </c>
       <c r="F59" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G59" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -2267,16 +2270,16 @@
         <v>117</v>
       </c>
       <c r="D60" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E60">
         <v>41</v>
       </c>
       <c r="F60" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G60" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -2290,16 +2293,16 @@
         <v>118</v>
       </c>
       <c r="D61" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E61">
         <v>50</v>
       </c>
       <c r="F61" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G61" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -2313,16 +2316,16 @@
         <v>119</v>
       </c>
       <c r="D62" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E62">
         <v>50</v>
       </c>
       <c r="F62" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G62" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -2336,16 +2339,16 @@
         <v>120</v>
       </c>
       <c r="D63" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E63">
         <v>60</v>
       </c>
       <c r="F63" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G63" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -2359,16 +2362,16 @@
         <v>121</v>
       </c>
       <c r="D64" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E64">
         <v>60</v>
       </c>
       <c r="F64" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G64" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -2382,16 +2385,16 @@
         <v>122</v>
       </c>
       <c r="D65" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E65">
         <v>40</v>
       </c>
       <c r="F65" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G65" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>

--- a/Teachers_and_School_Patrons_Extract.xlsx
+++ b/Teachers_and_School_Patrons_Extract.xlsx
@@ -1146,7 +1146,7 @@
         <v>125</v>
       </c>
       <c r="E11">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="F11" t="s">
         <v>175</v>
@@ -1169,7 +1169,7 @@
         <v>126</v>
       </c>
       <c r="E12">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="F12" t="s">
         <v>175</v>
@@ -1192,7 +1192,7 @@
         <v>127</v>
       </c>
       <c r="E13">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="F13" t="s">
         <v>175</v>
@@ -1215,7 +1215,7 @@
         <v>128</v>
       </c>
       <c r="E14">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
         <v>175</v>
@@ -1238,7 +1238,7 @@
         <v>129</v>
       </c>
       <c r="E15">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="F15" t="s">
         <v>175</v>

--- a/Teachers_and_School_Patrons_Extract.xlsx
+++ b/Teachers_and_School_Patrons_Extract.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="177">
   <si>
     <t>District</t>
   </si>
@@ -418,6 +418,9 @@
     <t>OMELU LAWRENCE</t>
   </si>
   <si>
+    <t>Kibet Aggrey and Ojom Samuel</t>
+  </si>
+  <si>
     <t>LLoyep Julius</t>
   </si>
   <si>
@@ -505,7 +508,7 @@
     <t>Loteng James and Cheptengan Leah</t>
   </si>
   <si>
-    <t>Tukei Clement and kaptengan Leonard</t>
+    <t>Tukei Clement and kaptengan Leonard / Tukei Clement and Leonard Kaptengan</t>
   </si>
   <si>
     <t>Kauke Laban, Mateba kennedy</t>
@@ -942,10 +945,10 @@
         <v>41</v>
       </c>
       <c r="F2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -965,10 +968,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -988,10 +991,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1011,10 +1014,10 @@
         <v>41</v>
       </c>
       <c r="F5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1034,10 +1037,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1057,10 +1060,10 @@
         <v>41</v>
       </c>
       <c r="F7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1080,10 +1083,10 @@
         <v>41</v>
       </c>
       <c r="F8" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1103,10 +1106,10 @@
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1126,10 +1129,10 @@
         <v>41</v>
       </c>
       <c r="F10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G10" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1149,10 +1152,10 @@
         <v>41</v>
       </c>
       <c r="F11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1172,10 +1175,10 @@
         <v>41</v>
       </c>
       <c r="F12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1195,10 +1198,10 @@
         <v>41</v>
       </c>
       <c r="F13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1218,10 +1221,10 @@
         <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1241,10 +1244,10 @@
         <v>41</v>
       </c>
       <c r="F15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1264,10 +1267,10 @@
         <v>30</v>
       </c>
       <c r="F16" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1287,10 +1290,10 @@
         <v>35</v>
       </c>
       <c r="F17" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G17" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1310,10 +1313,10 @@
         <v>41</v>
       </c>
       <c r="F18" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G18" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -1333,10 +1336,10 @@
         <v>41</v>
       </c>
       <c r="F19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G19" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -1356,10 +1359,10 @@
         <v>0</v>
       </c>
       <c r="F20" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G20" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -1373,16 +1376,16 @@
         <v>78</v>
       </c>
       <c r="D21" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F21" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G21" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -1396,16 +1399,16 @@
         <v>79</v>
       </c>
       <c r="D22" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E22">
         <v>41</v>
       </c>
       <c r="F22" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G22" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -1425,10 +1428,10 @@
         <v>0</v>
       </c>
       <c r="F23" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G23" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -1442,16 +1445,16 @@
         <v>81</v>
       </c>
       <c r="D24" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E24">
         <v>41</v>
       </c>
       <c r="F24" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G24" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -1471,10 +1474,10 @@
         <v>0</v>
       </c>
       <c r="F25" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G25" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -1488,16 +1491,16 @@
         <v>83</v>
       </c>
       <c r="D26" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E26">
         <v>30</v>
       </c>
       <c r="F26" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G26" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1511,16 +1514,16 @@
         <v>84</v>
       </c>
       <c r="D27" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E27">
         <v>30</v>
       </c>
       <c r="F27" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G27" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1534,16 +1537,16 @@
         <v>85</v>
       </c>
       <c r="D28" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E28">
         <v>41</v>
       </c>
       <c r="F28" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G28" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1557,16 +1560,16 @@
         <v>86</v>
       </c>
       <c r="D29" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E29">
         <v>41</v>
       </c>
       <c r="F29" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G29" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1580,16 +1583,16 @@
         <v>87</v>
       </c>
       <c r="D30" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E30">
         <v>41</v>
       </c>
       <c r="F30" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G30" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1603,16 +1606,16 @@
         <v>88</v>
       </c>
       <c r="D31" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E31">
         <v>41</v>
       </c>
       <c r="F31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1626,16 +1629,16 @@
         <v>89</v>
       </c>
       <c r="D32" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E32">
         <v>41</v>
       </c>
       <c r="F32" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G32" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1649,16 +1652,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E33">
         <v>41</v>
       </c>
       <c r="F33" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G33" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1672,16 +1675,16 @@
         <v>91</v>
       </c>
       <c r="D34" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E34">
         <v>41</v>
       </c>
       <c r="F34" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G34" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1695,16 +1698,16 @@
         <v>92</v>
       </c>
       <c r="D35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E35">
         <v>41</v>
       </c>
       <c r="F35" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G35" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1724,10 +1727,10 @@
         <v>0</v>
       </c>
       <c r="F36" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G36" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1741,16 +1744,16 @@
         <v>94</v>
       </c>
       <c r="D37" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E37">
         <v>41</v>
       </c>
       <c r="F37" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G37" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1770,10 +1773,10 @@
         <v>0</v>
       </c>
       <c r="F38" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G38" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1787,16 +1790,16 @@
         <v>96</v>
       </c>
       <c r="D39" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E39">
         <v>70</v>
       </c>
       <c r="F39" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G39" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1810,16 +1813,16 @@
         <v>97</v>
       </c>
       <c r="D40" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E40">
         <v>41</v>
       </c>
       <c r="F40" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G40" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1833,16 +1836,16 @@
         <v>98</v>
       </c>
       <c r="D41" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E41">
         <v>41</v>
       </c>
       <c r="F41" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G41" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1856,16 +1859,16 @@
         <v>99</v>
       </c>
       <c r="D42" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E42">
         <v>28</v>
       </c>
       <c r="F42" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G42" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1879,16 +1882,16 @@
         <v>100</v>
       </c>
       <c r="D43" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E43">
         <v>41</v>
       </c>
       <c r="F43" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G43" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1902,16 +1905,16 @@
         <v>101</v>
       </c>
       <c r="D44" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E44">
         <v>41</v>
       </c>
       <c r="F44" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G44" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1925,16 +1928,16 @@
         <v>102</v>
       </c>
       <c r="D45" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E45">
         <v>41</v>
       </c>
       <c r="F45" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G45" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1948,16 +1951,16 @@
         <v>103</v>
       </c>
       <c r="D46" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E46">
         <v>41</v>
       </c>
       <c r="F46" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G46" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1971,16 +1974,16 @@
         <v>104</v>
       </c>
       <c r="D47" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E47">
         <v>41</v>
       </c>
       <c r="F47" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G47" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1994,16 +1997,16 @@
         <v>105</v>
       </c>
       <c r="D48" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E48">
         <v>41</v>
       </c>
       <c r="F48" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G48" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -2017,16 +2020,16 @@
         <v>106</v>
       </c>
       <c r="D49" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E49">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F49" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G49" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -2040,16 +2043,16 @@
         <v>107</v>
       </c>
       <c r="D50" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E50">
         <v>41</v>
       </c>
       <c r="F50" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G50" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -2063,16 +2066,16 @@
         <v>108</v>
       </c>
       <c r="D51" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E51">
         <v>60</v>
       </c>
       <c r="F51" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G51" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -2086,16 +2089,16 @@
         <v>109</v>
       </c>
       <c r="D52" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E52">
         <v>60</v>
       </c>
       <c r="F52" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G52" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -2109,16 +2112,16 @@
         <v>110</v>
       </c>
       <c r="D53" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E53">
         <v>60</v>
       </c>
       <c r="F53" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G53" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -2132,16 +2135,16 @@
         <v>111</v>
       </c>
       <c r="D54" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E54">
         <v>55</v>
       </c>
       <c r="F54" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G54" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -2155,16 +2158,16 @@
         <v>112</v>
       </c>
       <c r="D55" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E55">
         <v>68</v>
       </c>
       <c r="F55" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G55" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -2178,16 +2181,16 @@
         <v>113</v>
       </c>
       <c r="D56" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E56">
         <v>41</v>
       </c>
       <c r="F56" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G56" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -2201,16 +2204,16 @@
         <v>114</v>
       </c>
       <c r="D57" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E57">
         <v>41</v>
       </c>
       <c r="F57" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G57" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -2224,16 +2227,16 @@
         <v>115</v>
       </c>
       <c r="D58" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E58">
         <v>41</v>
       </c>
       <c r="F58" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G58" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -2247,16 +2250,16 @@
         <v>116</v>
       </c>
       <c r="D59" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E59">
         <v>41</v>
       </c>
       <c r="F59" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G59" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -2270,16 +2273,16 @@
         <v>117</v>
       </c>
       <c r="D60" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E60">
         <v>41</v>
       </c>
       <c r="F60" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G60" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -2293,16 +2296,16 @@
         <v>118</v>
       </c>
       <c r="D61" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E61">
         <v>50</v>
       </c>
       <c r="F61" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G61" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -2316,16 +2319,16 @@
         <v>119</v>
       </c>
       <c r="D62" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E62">
         <v>50</v>
       </c>
       <c r="F62" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G62" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -2339,16 +2342,16 @@
         <v>120</v>
       </c>
       <c r="D63" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E63">
         <v>60</v>
       </c>
       <c r="F63" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G63" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -2362,16 +2365,16 @@
         <v>121</v>
       </c>
       <c r="D64" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E64">
         <v>60</v>
       </c>
       <c r="F64" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G64" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -2385,16 +2388,16 @@
         <v>122</v>
       </c>
       <c r="D65" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E65">
         <v>40</v>
       </c>
       <c r="F65" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G65" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
